--- a/ETF Regime mode/batchruns/batch_regime_filtered_strategy.xlsx
+++ b/ETF Regime mode/batchruns/batch_regime_filtered_strategy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="308" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="79" uniqueCount="78">
   <si>
     <t>Ticker</t>
   </si>
@@ -54,6 +54,9 @@
     <t>SellConfirmDays</t>
   </si>
   <si>
+    <t>RegimeRiskOffScale</t>
+  </si>
+  <si>
     <t>BuyHoldReturnPct</t>
   </si>
   <si>
@@ -187,6 +190,9 @@
   </si>
   <si>
     <t>SPYRegimeRiskOnPct</t>
+  </si>
+  <si>
+    <t>AverageRegimeScalePct</t>
   </si>
   <si>
     <t>BuyHoldExcessReturnPct</t>
@@ -286,7 +292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BU4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="true"/>
@@ -297,69 +303,71 @@
     <col min="6" max="6" width="6.9453125" customWidth="true"/>
     <col min="7" max="7" width="14.20703125" customWidth="true"/>
     <col min="8" max="8" width="13.9453125" customWidth="true"/>
-    <col min="9" max="9" width="15.5234375" customWidth="true"/>
-    <col min="10" max="10" width="15.3671875" customWidth="true"/>
-    <col min="11" max="11" width="16.1015625" customWidth="true"/>
-    <col min="12" max="12" width="15.5234375" customWidth="true"/>
-    <col min="13" max="13" width="20.68359375" customWidth="true"/>
-    <col min="14" max="14" width="22.3125" customWidth="true"/>
-    <col min="15" max="15" width="22.15625" customWidth="true"/>
-    <col min="16" max="16" width="22.89453125" customWidth="true"/>
-    <col min="17" max="17" width="22.3125" customWidth="true"/>
-    <col min="18" max="18" width="27.47265625" customWidth="true"/>
-    <col min="19" max="19" width="13.20703125" customWidth="true"/>
-    <col min="20" max="20" width="13.05078125" customWidth="true"/>
-    <col min="21" max="21" width="13.7890625" customWidth="true"/>
-    <col min="22" max="22" width="13.20703125" customWidth="true"/>
-    <col min="23" max="23" width="18.3671875" customWidth="true"/>
-    <col min="24" max="24" width="15.41796875" customWidth="true"/>
-    <col min="25" max="25" width="15.26171875" customWidth="true"/>
-    <col min="26" max="26" width="16" customWidth="true"/>
-    <col min="27" max="27" width="15.41796875" customWidth="true"/>
-    <col min="28" max="28" width="20.578125" customWidth="true"/>
-    <col min="29" max="29" width="15.15625" customWidth="true"/>
-    <col min="30" max="30" width="15" customWidth="true"/>
-    <col min="31" max="31" width="15.734375" customWidth="true"/>
-    <col min="32" max="32" width="15.15625" customWidth="true"/>
-    <col min="33" max="33" width="20.3125" customWidth="true"/>
-    <col min="34" max="34" width="16.99609375" customWidth="true"/>
-    <col min="35" max="35" width="16.83984375" customWidth="true"/>
-    <col min="36" max="36" width="17.578125" customWidth="true"/>
-    <col min="37" max="37" width="16.99609375" customWidth="true"/>
-    <col min="38" max="38" width="22.15625" customWidth="true"/>
-    <col min="39" max="39" width="21.3671875" customWidth="true"/>
-    <col min="40" max="40" width="21.20703125" customWidth="true"/>
-    <col min="41" max="41" width="21.9453125" customWidth="true"/>
-    <col min="42" max="42" width="21.3671875" customWidth="true"/>
-    <col min="43" max="43" width="26.5234375" customWidth="true"/>
-    <col min="44" max="44" width="17.20703125" customWidth="true"/>
-    <col min="45" max="45" width="23.83984375" customWidth="true"/>
-    <col min="46" max="46" width="29" customWidth="true"/>
-    <col min="47" max="47" width="19.5234375" customWidth="true"/>
-    <col min="48" max="48" width="24.1015625" customWidth="true"/>
-    <col min="49" max="49" width="27.20703125" customWidth="true"/>
-    <col min="50" max="50" width="25.41796875" customWidth="true"/>
-    <col min="51" max="51" width="14" customWidth="true"/>
-    <col min="52" max="52" width="21.734375" customWidth="true"/>
-    <col min="53" max="53" width="17.68359375" customWidth="true"/>
-    <col min="54" max="54" width="20.578125" customWidth="true"/>
-    <col min="55" max="55" width="20.41796875" customWidth="true"/>
-    <col min="56" max="56" width="21.15625" customWidth="true"/>
-    <col min="57" max="57" width="20.578125" customWidth="true"/>
-    <col min="58" max="58" width="25.734375" customWidth="true"/>
-    <col min="59" max="59" width="29.62890625" customWidth="true"/>
-    <col min="60" max="60" width="29.47265625" customWidth="true"/>
-    <col min="61" max="61" width="30.20703125" customWidth="true"/>
-    <col min="62" max="62" width="29.62890625" customWidth="true"/>
-    <col min="63" max="63" width="34.7890625" customWidth="true"/>
-    <col min="64" max="64" width="23.99609375" customWidth="true"/>
-    <col min="65" max="65" width="23.83984375" customWidth="true"/>
-    <col min="66" max="66" width="24.578125" customWidth="true"/>
-    <col min="67" max="67" width="23.99609375" customWidth="true"/>
-    <col min="68" max="68" width="29.15625" customWidth="true"/>
-    <col min="69" max="69" width="29.15625" customWidth="true"/>
-    <col min="70" max="70" width="43.26171875" customWidth="true"/>
-    <col min="71" max="71" width="37.62890625" customWidth="true"/>
+    <col min="9" max="9" width="16.578125" customWidth="true"/>
+    <col min="10" max="10" width="15.5234375" customWidth="true"/>
+    <col min="11" max="11" width="15.3671875" customWidth="true"/>
+    <col min="12" max="12" width="16.1015625" customWidth="true"/>
+    <col min="13" max="13" width="15.5234375" customWidth="true"/>
+    <col min="14" max="14" width="20.68359375" customWidth="true"/>
+    <col min="15" max="15" width="22.3125" customWidth="true"/>
+    <col min="16" max="16" width="22.15625" customWidth="true"/>
+    <col min="17" max="17" width="22.89453125" customWidth="true"/>
+    <col min="18" max="18" width="22.3125" customWidth="true"/>
+    <col min="19" max="19" width="27.47265625" customWidth="true"/>
+    <col min="20" max="20" width="13.20703125" customWidth="true"/>
+    <col min="21" max="21" width="13.05078125" customWidth="true"/>
+    <col min="22" max="22" width="13.7890625" customWidth="true"/>
+    <col min="23" max="23" width="13.20703125" customWidth="true"/>
+    <col min="24" max="24" width="18.3671875" customWidth="true"/>
+    <col min="25" max="25" width="15.41796875" customWidth="true"/>
+    <col min="26" max="26" width="15.26171875" customWidth="true"/>
+    <col min="27" max="27" width="16" customWidth="true"/>
+    <col min="28" max="28" width="15.41796875" customWidth="true"/>
+    <col min="29" max="29" width="20.578125" customWidth="true"/>
+    <col min="30" max="30" width="15.15625" customWidth="true"/>
+    <col min="31" max="31" width="15" customWidth="true"/>
+    <col min="32" max="32" width="15.734375" customWidth="true"/>
+    <col min="33" max="33" width="15.15625" customWidth="true"/>
+    <col min="34" max="34" width="20.3125" customWidth="true"/>
+    <col min="35" max="35" width="16.99609375" customWidth="true"/>
+    <col min="36" max="36" width="16.83984375" customWidth="true"/>
+    <col min="37" max="37" width="17.578125" customWidth="true"/>
+    <col min="38" max="38" width="16.99609375" customWidth="true"/>
+    <col min="39" max="39" width="22.15625" customWidth="true"/>
+    <col min="40" max="40" width="21.3671875" customWidth="true"/>
+    <col min="41" max="41" width="21.20703125" customWidth="true"/>
+    <col min="42" max="42" width="21.9453125" customWidth="true"/>
+    <col min="43" max="43" width="21.3671875" customWidth="true"/>
+    <col min="44" max="44" width="26.5234375" customWidth="true"/>
+    <col min="45" max="45" width="17.20703125" customWidth="true"/>
+    <col min="46" max="46" width="23.83984375" customWidth="true"/>
+    <col min="47" max="47" width="29" customWidth="true"/>
+    <col min="48" max="48" width="19.5234375" customWidth="true"/>
+    <col min="49" max="49" width="24.1015625" customWidth="true"/>
+    <col min="50" max="50" width="27.20703125" customWidth="true"/>
+    <col min="51" max="51" width="25.41796875" customWidth="true"/>
+    <col min="52" max="52" width="14" customWidth="true"/>
+    <col min="53" max="53" width="21.734375" customWidth="true"/>
+    <col min="54" max="54" width="17.68359375" customWidth="true"/>
+    <col min="55" max="55" width="19.89453125" customWidth="true"/>
+    <col min="56" max="56" width="20.578125" customWidth="true"/>
+    <col min="57" max="57" width="20.41796875" customWidth="true"/>
+    <col min="58" max="58" width="21.15625" customWidth="true"/>
+    <col min="59" max="59" width="20.578125" customWidth="true"/>
+    <col min="60" max="60" width="25.734375" customWidth="true"/>
+    <col min="61" max="61" width="29.62890625" customWidth="true"/>
+    <col min="62" max="62" width="29.47265625" customWidth="true"/>
+    <col min="63" max="63" width="30.20703125" customWidth="true"/>
+    <col min="64" max="64" width="29.62890625" customWidth="true"/>
+    <col min="65" max="65" width="34.7890625" customWidth="true"/>
+    <col min="66" max="66" width="23.99609375" customWidth="true"/>
+    <col min="67" max="67" width="23.83984375" customWidth="true"/>
+    <col min="68" max="68" width="24.578125" customWidth="true"/>
+    <col min="69" max="69" width="23.99609375" customWidth="true"/>
+    <col min="70" max="70" width="29.15625" customWidth="true"/>
+    <col min="71" max="71" width="29.15625" customWidth="true"/>
+    <col min="72" max="72" width="43.26171875" customWidth="true"/>
+    <col min="73" max="73" width="37.62890625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,6 +584,12 @@
       <c r="BS1" s="0" t="s">
         <v>75</v>
       </c>
+      <c r="BT1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="BU1" s="0" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -603,55 +617,55 @@
         <v>8</v>
       </c>
       <c r="I2" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="0">
         <v>339.63177562489244</v>
       </c>
-      <c r="J2" s="0">
+      <c r="K2" s="0">
         <v>432.28680471328511</v>
       </c>
-      <c r="K2" s="0">
+      <c r="L2" s="0">
         <v>419.30612603563463</v>
-      </c>
-      <c r="L2" s="0">
-        <v>432.28680471328511</v>
       </c>
       <c r="M2" s="0">
         <v>432.28680471328511</v>
       </c>
       <c r="N2" s="0">
+        <v>432.28680471328511</v>
+      </c>
+      <c r="O2" s="0">
         <v>-33.715385820778607</v>
       </c>
-      <c r="O2" s="0">
+      <c r="P2" s="0">
         <v>-24.073604766594158</v>
       </c>
-      <c r="P2" s="0">
+      <c r="Q2" s="0">
         <v>-24.497326364091077</v>
-      </c>
-      <c r="Q2" s="0">
-        <v>-24.073604766594158</v>
       </c>
       <c r="R2" s="0">
         <v>-24.073604766594158</v>
       </c>
       <c r="S2" s="0">
+        <v>-24.073604766594158</v>
+      </c>
+      <c r="T2" s="0">
         <v>0.82591294677085225</v>
       </c>
-      <c r="T2" s="0">
+      <c r="U2" s="0">
         <v>1.0279386507973149</v>
       </c>
-      <c r="U2" s="0">
+      <c r="V2" s="0">
         <v>1.017688926866156</v>
-      </c>
-      <c r="V2" s="0">
-        <v>1.0279386507973149</v>
       </c>
       <c r="W2" s="0">
         <v>1.0279386507973149</v>
       </c>
       <c r="X2" s="0">
+        <v>1.0279386507973149</v>
+      </c>
+      <c r="Y2" s="0">
         <v>1</v>
-      </c>
-      <c r="Y2" s="0">
-        <v>7</v>
       </c>
       <c r="Z2" s="0">
         <v>7</v>
@@ -663,10 +677,10 @@
         <v>7</v>
       </c>
       <c r="AC2" s="0">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD2" s="0">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="0">
         <v>6</v>
@@ -678,25 +692,25 @@
         <v>6</v>
       </c>
       <c r="AH2" s="0">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="0">
         <v>13</v>
       </c>
-      <c r="AJ2" s="0">
+      <c r="AK2" s="0">
         <v>35</v>
-      </c>
-      <c r="AK2" s="0">
-        <v>13</v>
       </c>
       <c r="AL2" s="0">
         <v>13</v>
       </c>
       <c r="AM2" s="0">
+        <v>13</v>
+      </c>
+      <c r="AN2" s="0">
         <v>100</v>
-      </c>
-      <c r="AN2" s="0">
-        <v>96.652719665271974</v>
       </c>
       <c r="AO2" s="0">
         <v>96.652719665271974</v>
@@ -708,87 +722,93 @@
         <v>96.652719665271974</v>
       </c>
       <c r="AR2" s="0">
+        <v>96.652719665271974</v>
+      </c>
+      <c r="AS2" s="0">
         <v>96.499302649930243</v>
-      </c>
-      <c r="AS2" s="0">
-        <v>96.652719665271974</v>
       </c>
       <c r="AT2" s="0">
         <v>96.652719665271974</v>
       </c>
       <c r="AU2" s="0">
+        <v>96.652719665271974</v>
+      </c>
+      <c r="AV2" s="0">
         <v>14.4</v>
       </c>
-      <c r="AV2" s="0">
+      <c r="AW2" s="0">
         <v>13</v>
       </c>
-      <c r="AW2" s="0">
+      <c r="AX2" s="0">
         <v>35</v>
       </c>
-      <c r="AX2" s="0">
+      <c r="AY2" s="0">
         <v>8</v>
       </c>
-      <c r="AY2" s="0">
+      <c r="AZ2" s="0">
         <v>1</v>
       </c>
-      <c r="AZ2" s="0">
+      <c r="BA2" s="0">
         <v>0.017180735930735932</v>
       </c>
-      <c r="BA2" s="0">
+      <c r="BB2" s="0">
         <v>96.652719665271974</v>
       </c>
-      <c r="BB2" s="0">
-        <v>0</v>
-      </c>
       <c r="BC2" s="0">
-        <v>92.655029088392652</v>
+        <v>98.326359832635973</v>
       </c>
       <c r="BD2" s="0">
-        <v>79.674350410742178</v>
+        <v>0</v>
       </c>
       <c r="BE2" s="0">
         <v>92.655029088392652</v>
       </c>
       <c r="BF2" s="0">
+        <v>79.674350410742178</v>
+      </c>
+      <c r="BG2" s="0">
         <v>92.655029088392652</v>
       </c>
-      <c r="BG2" s="0">
-        <v>0</v>
-      </c>
       <c r="BH2" s="0">
-        <v>9.6417810541844506</v>
+        <v>92.655029088392652</v>
       </c>
       <c r="BI2" s="0">
-        <v>9.2180594566875325</v>
+        <v>0</v>
       </c>
       <c r="BJ2" s="0">
         <v>9.6417810541844506</v>
       </c>
       <c r="BK2" s="0">
+        <v>9.2180594566875325</v>
+      </c>
+      <c r="BL2" s="0">
         <v>9.6417810541844506</v>
       </c>
-      <c r="BL2" s="0">
-        <v>0</v>
-      </c>
       <c r="BM2" s="0">
-        <v>0.20202570402646269</v>
+        <v>9.6417810541844506</v>
       </c>
       <c r="BN2" s="0">
-        <v>0.19177598009530372</v>
+        <v>0</v>
       </c>
       <c r="BO2" s="0">
         <v>0.20202570402646269</v>
       </c>
       <c r="BP2" s="0">
+        <v>0.19177598009530372</v>
+      </c>
+      <c r="BQ2" s="0">
         <v>0.20202570402646269</v>
       </c>
-      <c r="BQ2" s="0">
-        <v>0</v>
-      </c>
       <c r="BR2" s="0">
-        <v>0</v>
+        <v>0.20202570402646269</v>
       </c>
       <c r="BS2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BT2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BU2" s="0">
         <v>0</v>
       </c>
     </row>
@@ -818,55 +838,55 @@
         <v>8</v>
       </c>
       <c r="I3" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="0">
         <v>676.99257536452114</v>
       </c>
-      <c r="J3" s="0">
+      <c r="K3" s="0">
         <v>719.03877011519592</v>
-      </c>
-      <c r="K3" s="0">
-        <v>722.77091668471223</v>
       </c>
       <c r="L3" s="0">
         <v>722.77091668471223</v>
       </c>
       <c r="M3" s="0">
-        <v>699.42322784142607</v>
+        <v>722.77091668471223</v>
       </c>
       <c r="N3" s="0">
+        <v>711.44744884878855</v>
+      </c>
+      <c r="O3" s="0">
         <v>-35.119666881826539</v>
       </c>
-      <c r="O3" s="0">
+      <c r="P3" s="0">
         <v>-30.159087754807157</v>
-      </c>
-      <c r="P3" s="0">
-        <v>-30.150321939563472</v>
       </c>
       <c r="Q3" s="0">
         <v>-30.150321939563472</v>
       </c>
       <c r="R3" s="0">
-        <v>-30.150321939563419</v>
+        <v>-30.150321939563472</v>
       </c>
       <c r="S3" s="0">
+        <v>-30.150321939563508</v>
+      </c>
+      <c r="T3" s="0">
         <v>0.93436024338566648</v>
       </c>
-      <c r="T3" s="0">
+      <c r="U3" s="0">
         <v>1.0483454895318489</v>
-      </c>
-      <c r="U3" s="0">
-        <v>1.0542780345112299</v>
       </c>
       <c r="V3" s="0">
         <v>1.0542780345112299</v>
       </c>
       <c r="W3" s="0">
-        <v>1.0454592353772949</v>
+        <v>1.0542780345112299</v>
       </c>
       <c r="X3" s="0">
+        <v>1.0512254439174826</v>
+      </c>
+      <c r="Y3" s="0">
         <v>1</v>
-      </c>
-      <c r="Y3" s="0">
-        <v>10</v>
       </c>
       <c r="Z3" s="0">
         <v>10</v>
@@ -875,13 +895,13 @@
         <v>10</v>
       </c>
       <c r="AB3" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC3" s="0">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD3" s="0">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="0">
         <v>9</v>
@@ -890,28 +910,28 @@
         <v>9</v>
       </c>
       <c r="AG3" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH3" s="0">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="0">
         <v>19</v>
-      </c>
-      <c r="AJ3" s="0">
-        <v>45</v>
       </c>
       <c r="AK3" s="0">
         <v>45</v>
       </c>
       <c r="AL3" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AM3" s="0">
+        <v>47</v>
+      </c>
+      <c r="AN3" s="0">
         <v>100</v>
-      </c>
-      <c r="AN3" s="0">
-        <v>94.525801952580196</v>
       </c>
       <c r="AO3" s="0">
         <v>94.525801952580196</v>
@@ -920,91 +940,97 @@
         <v>94.525801952580196</v>
       </c>
       <c r="AQ3" s="0">
-        <v>94.037656903765694</v>
+        <v>94.525801952580196</v>
       </c>
       <c r="AR3" s="0">
-        <v>94.346234309623426</v>
+        <v>94.525801952580196</v>
       </c>
       <c r="AS3" s="0">
         <v>94.346234309623426</v>
       </c>
       <c r="AT3" s="0">
-        <v>93.922594142259413</v>
+        <v>94.346234309623426</v>
       </c>
       <c r="AU3" s="0">
+        <v>94.134414225941427</v>
+      </c>
+      <c r="AV3" s="0">
         <v>20.200000000000003</v>
       </c>
-      <c r="AV3" s="0">
-        <v>23.200000000000003</v>
-      </c>
       <c r="AW3" s="0">
+        <v>21.700000000000003</v>
+      </c>
+      <c r="AX3" s="0">
         <v>45</v>
       </c>
-      <c r="AX3" s="0">
+      <c r="AY3" s="0">
         <v>6</v>
       </c>
-      <c r="AY3" s="0">
+      <c r="AZ3" s="0">
         <v>1</v>
       </c>
-      <c r="AZ3" s="0">
+      <c r="BA3" s="0">
         <v>0.021255994098118774</v>
       </c>
-      <c r="BA3" s="0">
+      <c r="BB3" s="0">
         <v>96.652719665271974</v>
       </c>
-      <c r="BB3" s="0">
-        <v>0</v>
-      </c>
       <c r="BC3" s="0">
+        <v>98.326359832635973</v>
+      </c>
+      <c r="BD3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="0">
         <v>42.046194750674815</v>
       </c>
-      <c r="BD3" s="0">
+      <c r="BF3" s="0">
         <v>45.778341320191096</v>
       </c>
-      <c r="BE3" s="0">
+      <c r="BG3" s="0">
         <v>45.778341320191096</v>
       </c>
-      <c r="BF3" s="0">
-        <v>22.430652476904989</v>
-      </c>
-      <c r="BG3" s="0">
-        <v>0</v>
-      </c>
       <c r="BH3" s="0">
+        <v>34.454873484267523</v>
+      </c>
+      <c r="BI3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="0">
         <v>4.9605791270193826</v>
       </c>
-      <c r="BI3" s="0">
+      <c r="BK3" s="0">
         <v>4.9693449422630653</v>
       </c>
-      <c r="BJ3" s="0">
+      <c r="BL3" s="0">
         <v>4.9693449422630653</v>
       </c>
-      <c r="BK3" s="0">
-        <v>4.9693449422631204</v>
-      </c>
-      <c r="BL3" s="0">
-        <v>0</v>
-      </c>
       <c r="BM3" s="0">
+        <v>4.9693449422630316</v>
+      </c>
+      <c r="BN3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BO3" s="0">
         <v>0.11398524614618244</v>
       </c>
-      <c r="BN3" s="0">
+      <c r="BP3" s="0">
         <v>0.11991779112556344</v>
       </c>
-      <c r="BO3" s="0">
+      <c r="BQ3" s="0">
         <v>0.11991779112556344</v>
       </c>
-      <c r="BP3" s="0">
-        <v>0.11109899199162843</v>
-      </c>
-      <c r="BQ3" s="0">
-        <v>-23.347688843286107</v>
-      </c>
       <c r="BR3" s="0">
-        <v>5.5511151231257827e-14</v>
+        <v>0.11686520053181615</v>
       </c>
       <c r="BS3" s="0">
-        <v>-0.008818799133935018</v>
+        <v>-11.323467835923573</v>
+      </c>
+      <c r="BT3" s="0">
+        <v>-3.3306690738754696e-14</v>
+      </c>
+      <c r="BU3" s="0">
+        <v>-0.0030525905937472952</v>
       </c>
     </row>
     <row r="4">
@@ -1033,55 +1059,55 @@
         <v>8</v>
       </c>
       <c r="I4" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="0">
         <v>456.72653958944289</v>
       </c>
-      <c r="J4" s="0">
+      <c r="K4" s="0">
         <v>621.94971594098104</v>
-      </c>
-      <c r="K4" s="0">
-        <v>623.78802580871377</v>
       </c>
       <c r="L4" s="0">
         <v>623.78802580871377</v>
       </c>
       <c r="M4" s="0">
-        <v>618.25191206909437</v>
+        <v>623.78802580871377</v>
       </c>
       <c r="N4" s="0">
+        <v>621.24783714851037</v>
+      </c>
+      <c r="O4" s="0">
         <v>-32.676170186531131</v>
       </c>
-      <c r="O4" s="0">
+      <c r="P4" s="0">
         <v>-24.718937424899057</v>
-      </c>
-      <c r="P4" s="0">
-        <v>-24.297892635989349</v>
       </c>
       <c r="Q4" s="0">
         <v>-24.297892635989349</v>
       </c>
       <c r="R4" s="0">
-        <v>-24.29789263598936</v>
+        <v>-24.297892635989349</v>
       </c>
       <c r="S4" s="0">
+        <v>-24.297892635989349</v>
+      </c>
+      <c r="T4" s="0">
         <v>0.85109775601218884</v>
       </c>
-      <c r="T4" s="0">
+      <c r="U4" s="0">
         <v>1.0845880660396914</v>
-      </c>
-      <c r="U4" s="0">
-        <v>1.0888466791820974</v>
       </c>
       <c r="V4" s="0">
         <v>1.0888466791820974</v>
       </c>
       <c r="W4" s="0">
-        <v>1.0884939166738485</v>
+        <v>1.0888466791820974</v>
       </c>
       <c r="X4" s="0">
+        <v>1.0897126034097038</v>
+      </c>
+      <c r="Y4" s="0">
         <v>1</v>
-      </c>
-      <c r="Y4" s="0">
-        <v>9</v>
       </c>
       <c r="Z4" s="0">
         <v>9</v>
@@ -1090,13 +1116,13 @@
         <v>9</v>
       </c>
       <c r="AB4" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4" s="0">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD4" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="0">
         <v>8</v>
@@ -1105,16 +1131,16 @@
         <v>8</v>
       </c>
       <c r="AG4" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH4" s="0">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="0">
         <v>17</v>
-      </c>
-      <c r="AJ4" s="0">
-        <v>42</v>
       </c>
       <c r="AK4" s="0">
         <v>42</v>
@@ -1123,10 +1149,10 @@
         <v>42</v>
       </c>
       <c r="AM4" s="0">
+        <v>45</v>
+      </c>
+      <c r="AN4" s="0">
         <v>100</v>
-      </c>
-      <c r="AN4" s="0">
-        <v>94.735006973500703</v>
       </c>
       <c r="AO4" s="0">
         <v>94.735006973500703</v>
@@ -1135,91 +1161,97 @@
         <v>94.735006973500703</v>
       </c>
       <c r="AQ4" s="0">
-        <v>94.421199442119942</v>
+        <v>94.735006973500703</v>
       </c>
       <c r="AR4" s="0">
-        <v>94.548465829846577</v>
+        <v>94.735006973500703</v>
       </c>
       <c r="AS4" s="0">
         <v>94.548465829846577</v>
       </c>
       <c r="AT4" s="0">
-        <v>94.260808926080898</v>
+        <v>94.548465829846577</v>
       </c>
       <c r="AU4" s="0">
+        <v>94.404637377963738</v>
+      </c>
+      <c r="AV4" s="0">
         <v>18.5</v>
       </c>
-      <c r="AV4" s="0">
-        <v>20</v>
-      </c>
       <c r="AW4" s="0">
+        <v>19.25</v>
+      </c>
+      <c r="AX4" s="0">
         <v>42</v>
       </c>
-      <c r="AX4" s="0">
+      <c r="AY4" s="0">
         <v>6</v>
       </c>
-      <c r="AY4" s="0">
+      <c r="AZ4" s="0">
         <v>1</v>
       </c>
-      <c r="AZ4" s="0">
+      <c r="BA4" s="0">
         <v>0.02401545822598454</v>
       </c>
-      <c r="BA4" s="0">
+      <c r="BB4" s="0">
         <v>96.652719665271974</v>
       </c>
-      <c r="BB4" s="0">
-        <v>0</v>
-      </c>
       <c r="BC4" s="0">
+        <v>98.326359832635973</v>
+      </c>
+      <c r="BD4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="0">
         <v>165.22317635153811</v>
       </c>
-      <c r="BD4" s="0">
+      <c r="BF4" s="0">
         <v>167.06148621927088</v>
       </c>
-      <c r="BE4" s="0">
+      <c r="BG4" s="0">
         <v>167.06148621927088</v>
       </c>
-      <c r="BF4" s="0">
-        <v>161.52537247965145</v>
-      </c>
-      <c r="BG4" s="0">
-        <v>0</v>
-      </c>
       <c r="BH4" s="0">
+        <v>164.52129755906748</v>
+      </c>
+      <c r="BI4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="0">
         <v>7.9572327616320715</v>
       </c>
-      <c r="BI4" s="0">
+      <c r="BK4" s="0">
         <v>8.3782775505417799</v>
       </c>
-      <c r="BJ4" s="0">
+      <c r="BL4" s="0">
         <v>8.3782775505417799</v>
       </c>
-      <c r="BK4" s="0">
-        <v>8.3782775505417675</v>
-      </c>
-      <c r="BL4" s="0">
-        <v>0</v>
-      </c>
       <c r="BM4" s="0">
+        <v>8.3782775505417799</v>
+      </c>
+      <c r="BN4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BO4" s="0">
         <v>0.23349031002750253</v>
       </c>
-      <c r="BN4" s="0">
+      <c r="BP4" s="0">
         <v>0.23774892316990859</v>
       </c>
-      <c r="BO4" s="0">
+      <c r="BQ4" s="0">
         <v>0.23774892316990859</v>
       </c>
-      <c r="BP4" s="0">
-        <v>0.23739616066165969</v>
-      </c>
-      <c r="BQ4" s="0">
-        <v>-5.5361137396194415</v>
-      </c>
       <c r="BR4" s="0">
-        <v>-1.1102230246251565e-14</v>
+        <v>0.23861484739751493</v>
       </c>
       <c r="BS4" s="0">
-        <v>-0.00035276250824889388</v>
+        <v>-2.5401886602034018</v>
+      </c>
+      <c r="BT4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BU4" s="0">
+        <v>0.00086592422760634058</v>
       </c>
     </row>
   </sheetData>
